--- a/02_加值成品/八上/八上6-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上6-4_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上6-4 化合物的形成　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上6-4 化合物的形成　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>原子失去電子形成？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Na⁺</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>分子化合物</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>陽離子</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>陰離子</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>帶正電</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>原子得到電子形成？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>陰離子</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>NaCl</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>分子化合物</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Na⁺</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>帶負電</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>正負離子靜電結合成？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>離子化合物</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>Cl⁻</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Na⁺</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>下標</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>如NaCl</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>非金屬共用電子形成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>分子化合物</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>分子</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Na⁺</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>下標</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>如H₂O</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>食鹽的化學式是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>離子化合物</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>離子</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>不帶電</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>NaCl</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>離子</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>水的化學式是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>H₂O</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>Mg²⁺</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>CO₂</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>2個</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>分子</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>化學式數字寫在？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>離子化合物</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Na⁺</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>分子</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>下標</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>原子數</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>H₂O中有幾個氫原子？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>CO₂</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>H₂O</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>2個</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>下標2</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>原子得或失電子後帶電稱為？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>離子</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>不帶電</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>分子化合物</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>NaCl</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>離子</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>二氧化碳的化學式是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>2個</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>H₂O</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>CO₂</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>分子</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上6-4 化合物的形成　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上6-4 化合物的形成　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>鈉原子失1電子成？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>陰離子</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Na⁺</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>不帶電</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>下標</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>陽離子</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>氯原子得1電子成？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>離子化合物</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>不帶電</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Cl⁻</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>陽離子</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>陰離子</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>CO₂中有幾個氧原子？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>2個</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>CO₂</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>H₂O</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Mg²⁺</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>下標2</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>金屬與非金屬多形成哪類化合物？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>NaCl</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>離子化合物</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>不帶電</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>陽離子</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>得失電子</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>NaCl由哪兩種離子組成？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>共用電子vs得失電子</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Mg²⁺需2個Cl⁻平衡</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>3種(H、S、O)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Na⁺與Cl⁻</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>靜電結合</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>二氧化碳是離子還分子化合物？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>陰離子</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>分子化合物</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>下標</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>分子</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>共用電子</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>化合物整體帶電嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>分子</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>陽離子</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>不帶電</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>離子化合物</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>電荷平衡</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>H₂SO₄中共有幾種元素？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>正負電量相等使整體中性</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>正負電荷總和為零</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>3種(H、S、O)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>鈉給電子給氯,成Na⁺Cl⁻靜電結合</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>讀式</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>鎂原子失去2個電子形成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2個</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Mg²⁺</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>CO₂</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>陽離子</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>H₂O中氫與氧原子數比？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Mg²⁺</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>2個</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>H₂O</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>化學式</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上6-4 化合物的形成　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上6-4 化合物的形成　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>鈉與氯如何形成食鹽？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>共用電子vs得失電子</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>3種(H、S、O)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>鈉給電子給氯,成Na⁺Cl⁻靜電結合</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Na⁺與Cl⁻</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>電子轉移</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>離子化合物與分子化合物導電性差異？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Mg²⁺需2個Cl⁻平衡</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>3種(H、S、O)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Na⁺與Cl⁻</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>離子化合物溶於水可導電</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>電解質</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>為何離子化合物電荷須平衡？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Na⁺與Cl⁻</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>3種(H、S、O)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Mg²⁺需2個Cl⁻平衡</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>正負電量相等使整體中性</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>MgCl₂中鎂帶何電?為何要2個Cl?</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Mg²⁺需2個Cl⁻平衡</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>離子化合物溶於水可導電</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>3種(H、S、O)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>共用電子vs得失電子</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>電荷平衡</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>共價鍵與離子鍵最大差別？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Na⁺與Cl⁻</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>共用電子vs得失電子</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>鈉給電子給氯,成Na⁺Cl⁻靜電結合</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>各失得1電子電荷平衡</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>鍵結</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>化學式Ca(OH)₂含幾個氧？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>2個</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Mg²⁺</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>H₂O</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>括號×下標</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>水通常以分子或離子存在？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>離子化合物</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>分子化合物</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>離子</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>分子</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>共價</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>判斷化合物中性可用什麼？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>正負電荷總和為零</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>前者得失電子後者共用電子</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>共用電子vs得失電子</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>各失得1電子電荷平衡</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>電荷</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>離子化合物與分子化合物形成方式差別？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>前者得失電子後者共用電子</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>共用電子vs得失電子</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>3種(H、S、O)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Mg²⁺需2個Cl⁻平衡</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>鍵結</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何NaCl中Na與Cl以1:1結合？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>前者得失電子後者共用電子</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>各失得1電子電荷平衡</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Na⁺與Cl⁻</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>鈉給電子給氯,成Na⁺Cl⁻靜電結合</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>平衡</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上6-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上6-4_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>帶正電</t>
+          <t>帶正電：原子失去帶負電的電子後，正電荷比負電荷多，整體帶正電，形成陽離子</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>帶負電</t>
+          <t>帶負電：原子得到額外的電子後，負電荷比正電荷多，整體帶負電，形成陰離子</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>如NaCl</t>
+          <t>如NaCl：帶正電的陽離子和帶負電的陰離子之間靠靜電力互相吸引結合，形成離子化合物，例如食鹽NaCl</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>如H₂O</t>
+          <t>如H₂O：非金屬原子之間常靠共用電子對的方式結合成鍵，形成分子化合物，例如水H₂O</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>離子</t>
+          <t>離子：食鹽是由鈉離子和氯離子以1比1比例結合而成的離子化合物，化學式寫作NaCl</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>分子</t>
+          <t>分子：水分子由2個氫原子和1個氧原子共用電子結合而成，化學式寫作H₂O</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>原子數</t>
+          <t>原子數：化學式中表示原子個數的數字要寫在元素符號的右下方，稱為下標</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>下標2</t>
+          <t>下標2：H右下方的下標數字2，代表水分子中含有2個氫原子</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>離子</t>
+          <t>離子：原子得到或失去電子後，正負電荷不再平衡，整體帶電，這種帶電的粒子稱為離子</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>分子</t>
+          <t>分子：二氧化碳分子由1個碳原子和2個氧原子組成，化學式寫作CO₂</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>陽離子</t>
+          <t>陽離子：鈉原子失去1個帶負電的電子後，整體多了1個正電荷，形成鈉離子Na⁺</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>陰離子</t>
+          <t>陰離子：氯原子得到1個帶負電的電子後，整體多了1個負電荷，形成氯離子Cl⁻</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>下標2</t>
+          <t>下標2：CO₂中O右下方的下標數字2，代表二氧化碳分子中含有2個氧原子</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>得失電子</t>
+          <t>得失電子：金屬原子容易失去電子形成陽離子，非金屬原子容易得到電子形成陰離子，兩者結合時常靠得失電子形成離子化合物</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>靜電結合</t>
+          <t>靜電結合：食鹽NaCl是由帶正電的鈉離子(Na⁺)和帶負電的氯離子(Cl⁻)，靠靜電吸引力結合而成</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>共用電子</t>
+          <t>共用電子：二氧化碳中的碳原子和氧原子是靠共用電子對的方式結合成鍵，屬於分子化合物</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>電荷平衡</t>
+          <t>電荷平衡：不論是離子化合物還是分子化合物，正負電荷總和都會互相抵消，整體呈電中性，不帶電</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>讀式</t>
+          <t>讀式：H₂SO₄這個化學式中出現了氫(H)、硫(S)、氧(O)三種不同的元素符號，所以含有3種元素</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>陽離子</t>
+          <t>陽離子：鎂原子失去2個帶負電的電子後，整體帶2個正電荷，形成鎂離子Mg²⁺，屬於陽離子</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>化學式</t>
+          <t>化學式：水的化學式H₂O表示每個水分子含有2個氫原子和1個氧原子，原子數比是2比1</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>電子轉移</t>
+          <t>電子轉移：鈉原子把最外層的1個電子轉移給氯原子，鈉因此形成帶正電的Na⁺、氯形成帶負電的Cl⁻，兩種離子再靠靜電力互相吸引結合成食鹽</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>電解質</t>
+          <t>電解質：離子化合物溶於水後會解離出可自由移動的離子，能夠導電；多數分子化合物溶於水不會解離出離子，通常不導電</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：離子化合物是由帶電的陽離子和陰離子組成，整體必須保持電中性，所以正電荷總量一定要等於負電荷總量才能穩定結合</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>電荷平衡</t>
+          <t>電荷平衡：鎂原子失去2個電子形成帶2個正電荷的Mg²⁺，需要2個各帶1個負電荷的Cl⁻才能使正負電荷數量相等，達到電荷平衡</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>鍵結</t>
+          <t>鍵結：共價鍵是原子之間共用電子對來結合；離子鍵則是原子之間發生電子得失、形成帶電離子後再靠靜電力結合，兩者的鍵結方式完全不同</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>括號×下標</t>
+          <t>括號×下標：括號(OH)右下方的下標2表示括號內的OH整組要乘以2，OH裡本來就有1個氧，乘以2後共有2個氧原子</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>共價</t>
+          <t>共價：水分子是氫、氧原子以共價鍵(共用電子)結合而成的中性分子，平常大多以完整的水分子形式存在，只有極少量會解離成離子</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>電荷</t>
+          <t>電荷：檢查化合物中所有正電荷(如陽離子或元素的正化合價)總和是否等於所有負電荷總和，兩者相減為零就代表整個化合物呈電中性</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>鍵結</t>
+          <t>鍵結：離子化合物是由原子互相得失電子、形成帶正負電的離子後再靠靜電吸引力結合而成；分子化合物則是原子之間共用電子對形成共價鍵結合而成，兩者鍵結方式不同</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：鈉原子失去1個電子形成Na⁺，氯原子得到1個電子形成Cl⁻，兩者所帶的電荷數量相等、電性相反，需要以1比1的比例結合才能使整體電荷平衡</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上6-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上6-4_三種難度測驗卷.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Na⁺</t>
+          <t>陰離子</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>分子化合物</t>
+          <t>NaCl</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>陰離子</t>
+          <t>下標</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>Cl⁻</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
           <t>NaCl</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>分子化合物</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Cl⁻</t>
+          <t>分子化合物</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>下標</t>
+          <t>陰離子</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>分子</t>
+          <t>Na⁺</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Na⁺</t>
+          <t>離子化合物</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>下標</t>
+          <t>Cl⁻</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>不帶電</t>
+          <t>分子化合物</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>分子化合物</t>
+          <t>Na⁺</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>NaCl</t>
+          <t>陽離子</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>不帶電</t>
+          <t>下標</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>陽離子</t>
+          <t>Cl⁻</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>陰離子</t>
+          <t>不帶電</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>分子</t>
+          <t>離子</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>Na⁺</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>陰離子</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>離子化合物</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>分子化合物</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>離子</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
